--- a/DockFlow-SDS-Scenario-Pack/01-direct-accept-one-truck.xlsx
+++ b/DockFlow-SDS-Scenario-Pack/01-direct-accept-one-truck.xlsx
@@ -1,16 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\Unilever Projects\7th Project\DockFlow-SDS-Scenario-Pack\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Delivery Schedule" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Delivery Schedule" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
@@ -22,122 +26,102 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
   <si>
-    <t xml:space="preserve">Supplier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Material Code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UOM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delivery Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delivery Time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">End Time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remarks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ajinomoto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDS-ONE-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One-truck test material A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dressings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO-SDS-ONE-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supplier: accept with one truck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDS-ONE-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One-truck test material B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO-SDS-ONE-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantities should be locked in one-truck mode</t>
+    <t>Supplier</t>
+  </si>
+  <si>
+    <t>Material Code</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>UOM</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Delivery Date</t>
+  </si>
+  <si>
+    <t>Delivery Time</t>
+  </si>
+  <si>
+    <t>End Time</t>
+  </si>
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>PO Number</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>Ajinomoto</t>
+  </si>
+  <si>
+    <t>SDS-ONE-001</t>
+  </si>
+  <si>
+    <t>One-truck test material A</t>
+  </si>
+  <si>
+    <t>KG</t>
+  </si>
+  <si>
+    <t>Dressings</t>
+  </si>
+  <si>
+    <t>PO-SDS-ONE-001</t>
+  </si>
+  <si>
+    <t>Supplier: accept with one truck</t>
+  </si>
+  <si>
+    <t>SDS-ONE-002</t>
+  </si>
+  <si>
+    <t>One-truck test material B</t>
+  </si>
+  <si>
+    <t>PO-SDS-ONE-002</t>
+  </si>
+  <si>
+    <t>Quantities should be locked in one-truck mode</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="167" formatCode="hh:mm"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="hh:mm"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF172033"/>
       <name val="Calibri"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -156,134 +140,134 @@
     </fill>
   </fills>
   <borders count="10">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFB8C5D6"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9E1EA"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB8C5D6"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9E1EA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFD9E1EA"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9E1EA"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB8C5D6"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9E1EA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFD9E1EA"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB8C5D6"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB8C5D6"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9E1EA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFB8C5D6"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9E1EA"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9E1EA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9E1EA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFD9E1EA"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9E1EA"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9E1EA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9E1EA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFD9E1EA"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB8C5D6"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9E1EA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9E1EA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFB8C5D6"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9E1EA"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9E1EA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB8C5D6"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFD9E1EA"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9E1EA"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9E1EA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB8C5D6"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
+      <left style="thin">
+        <color rgb="FFB8C5D6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9E1EA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB8C5D6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9E1EA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9E1EA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9E1EA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB8C5D6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9E1EA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9E1EA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB8C5D6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB8C5D6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9E1EA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB8C5D6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9E1EA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9E1EA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9E1EA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9E1EA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9E1EA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9E1EA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9E1EA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9E1EA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB8C5D6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9E1EA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9E1EA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB8C5D6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9E1EA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9E1EA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8C5D6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9E1EA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9E1EA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9E1EA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8C5D6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFD9E1EA"/>
       </left>
@@ -299,110 +283,64 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="21">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="3" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="5" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="5" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="8" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="8" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="8" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="9" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Normal" xfId="20"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -461,13 +399,29 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF172033"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChatGPT">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
   <a:themeElements>
     <a:clrScheme name="ChatGPT">
       <a:dk1>
@@ -509,14 +463,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Calibri Light" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Calibri Light" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Calibri" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -546,7 +500,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -570,7 +524,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -627,35 +581,34 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="44"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -690,7 +643,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
@@ -703,17 +656,17 @@
       <c r="D2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="E2" s="6">
         <v>100</v>
       </c>
-      <c r="F2" s="7" t="n">
-        <v>46286.5</v>
-      </c>
-      <c r="G2" s="8" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="H2" s="8" t="n">
-        <v>0.458333333333333</v>
+      <c r="F2" s="7">
+        <v>46278.5</v>
+      </c>
+      <c r="G2" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="H2" s="8">
+        <v>0.45833333333333298</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>15</v>
@@ -725,7 +678,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
         <v>11</v>
       </c>
@@ -738,17 +691,17 @@
       <c r="D3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="12" t="n">
+      <c r="E3" s="12">
         <v>200</v>
       </c>
-      <c r="F3" s="13" t="n">
-        <v>46286.5</v>
-      </c>
-      <c r="G3" s="14" t="n">
+      <c r="F3" s="13">
+        <v>46278.5</v>
+      </c>
+      <c r="G3" s="14">
         <v>0.375</v>
       </c>
-      <c r="H3" s="14" t="n">
-        <v>0.458333333333333</v>
+      <c r="H3" s="14">
+        <v>0.45833333333333298</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>15</v>
@@ -761,12 +714,7 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>